--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84ba3aa2b9189868/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gupta\projects\Measuring-Gender-Bias-in-T2I-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{A48200C9-D2E0-44EC-ACB0-87ACB888FDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E028D8F-7A0E-41F6-9912-5A7F6736EB0A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED148C0-535C-420B-AF17-EAAB46C20BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D54C0805-13F8-4D75-8968-444619B3BB03}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{D54C0805-13F8-4D75-8968-444619B3BB03}"/>
   </bookViews>
   <sheets>
     <sheet name="prompts" sheetId="1" r:id="rId1"/>
@@ -951,10 +951,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1257,7 +1253,7 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="66.88671875" customWidth="1"/>
     <col min="2" max="2" width="9.5546875" customWidth="1"/>
     <col min="3" max="3" width="53.77734375" customWidth="1"/>
     <col min="4" max="4" width="60" customWidth="1"/>
